--- a/06-Employee Analytics & Insights/HR_DataAnalysis.xlsx
+++ b/06-Employee Analytics & Insights/HR_DataAnalysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hetal\OneDrive\Desktop\Data Analysis\HR_Salary_Analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65882454-A12F-411E-B195-F33127895623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA750DF9-859B-4E28-B2F9-C896D70C15CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Emp Attrition Analysis - Summry" sheetId="11" r:id="rId1"/>
@@ -17175,13 +17175,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>129539</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
+      <xdr:rowOff>32385</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>381000</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -17196,7 +17196,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="129539" y="22860"/>
+          <a:off x="129539" y="32385"/>
           <a:ext cx="3909061" cy="1358265"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
